--- a/data/b2_indio/B2 Índio 04-2026.xlsx
+++ b/data/b2_indio/B2 Índio 04-2026.xlsx
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>51315.84</v>
+        <v>51329.67</v>
       </c>
     </row>
     <row r="3">
@@ -4743,61 +4743,61 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2230.36</v>
+        <v>2170.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1666.46</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1794.94</v>
+        <v>1916.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3900</v>
+        <v>3206.24</v>
       </c>
     </row>
     <row r="7">
@@ -4806,70 +4806,70 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1162.53</v>
+        <v>1948.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3020.11</v>
+        <v>1372.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1772.02</v>
+        <v>9241.469999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1812.16</v>
+        <v>1432.31</v>
       </c>
     </row>
     <row r="11">
@@ -4878,34 +4878,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>9174.440000000001</v>
+        <v>1831.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1400.47</v>
+        <v>2241.38</v>
       </c>
     </row>
     <row r="13">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3338.71</v>
+        <v>3110.66</v>
       </c>
     </row>
     <row r="14">
@@ -4941,12 +4941,12 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>18362.63</v>
+        <v>18196.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3983.19</v>
+        <v>3435.48</v>
       </c>
     </row>
     <row r="16">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2918.73</v>
+        <v>3042.74</v>
       </c>
     </row>
     <row r="17">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1770.55</v>
+        <v>1780.5</v>
       </c>
     </row>
   </sheetData>
